--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92540758078</v>
+        <v>46157.93115026155</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115026155</v>
+        <v>46157.93368771146</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93368771146</v>
+        <v>46157.93672775204</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93672775204</v>
+        <v>46158.28194806702</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28194806702</v>
+        <v>46158.29718999573</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29718999573</v>
+        <v>46158.29791035963</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29791035963</v>
+        <v>46158.33356338285</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33356338285</v>
+        <v>46158.37211057252</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/20. СТО Каприз (ИП Новик В.В.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211057252</v>
+        <v>46158.37268027732</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
